--- a/tests/data/synthetic-cells/cells-1904.xlsx
+++ b/tests/data/synthetic-cells/cells-1904.xlsx
@@ -258,6 +258,9 @@
       <c r="L1" s="0">
         <v>0.999999999</v>
       </c>
+      <c r="M1" s="0">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
@@ -296,6 +299,9 @@
       <c r="L2" s="1">
         <v>0.999999999</v>
       </c>
+      <c r="M2" s="1">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
@@ -334,6 +340,9 @@
       <c r="L3" s="2">
         <v>0.999999999</v>
       </c>
+      <c r="M3" s="2">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
@@ -372,6 +381,9 @@
       <c r="L4" s="3">
         <v>0.999999999</v>
       </c>
+      <c r="M4" s="3">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4">
@@ -410,6 +422,9 @@
       <c r="L5" s="4">
         <v>0.999999999</v>
       </c>
+      <c r="M5" s="4">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5">
@@ -448,6 +463,9 @@
       <c r="L6" s="5">
         <v>0.999999999</v>
       </c>
+      <c r="M6" s="5">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6">
@@ -486,6 +504,9 @@
       <c r="L7" s="6">
         <v>0.999999999</v>
       </c>
+      <c r="M7" s="6">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7">
@@ -524,6 +545,9 @@
       <c r="L8" s="7">
         <v>0.999999999</v>
       </c>
+      <c r="M8" s="7">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8">
@@ -562,6 +586,9 @@
       <c r="L9" s="8">
         <v>0.999999999</v>
       </c>
+      <c r="M9" s="8">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
@@ -600,6 +627,9 @@
       <c r="L10" s="9">
         <v>0.999999999</v>
       </c>
+      <c r="M10" s="9">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10">
@@ -638,6 +668,9 @@
       <c r="L11" s="10">
         <v>0.999999999</v>
       </c>
+      <c r="M11" s="10">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11">
@@ -676,6 +709,9 @@
       <c r="L12" s="11">
         <v>0.999999999</v>
       </c>
+      <c r="M12" s="11">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="12">
@@ -714,6 +750,9 @@
       <c r="L13" s="12">
         <v>0.999999999</v>
       </c>
+      <c r="M13" s="12">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13">
@@ -752,6 +791,9 @@
       <c r="L14" s="13">
         <v>0.999999999</v>
       </c>
+      <c r="M14" s="13">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14">
@@ -790,6 +832,9 @@
       <c r="L15" s="14">
         <v>0.999999999</v>
       </c>
+      <c r="M15" s="14">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15">
@@ -828,6 +873,9 @@
       <c r="L16" s="15">
         <v>0.999999999</v>
       </c>
+      <c r="M16" s="15">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16">
@@ -866,6 +914,9 @@
       <c r="L17" s="16">
         <v>0.999999999</v>
       </c>
+      <c r="M17" s="16">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17">
@@ -904,6 +955,9 @@
       <c r="L18" s="17">
         <v>0.999999999</v>
       </c>
+      <c r="M18" s="17">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18">
@@ -942,6 +996,9 @@
       <c r="L19" s="18">
         <v>0.999999999</v>
       </c>
+      <c r="M19" s="18">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="19">
@@ -980,6 +1037,9 @@
       <c r="L20" s="19">
         <v>0.999999999</v>
       </c>
+      <c r="M20" s="19">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20">
@@ -1018,6 +1078,9 @@
       <c r="L21" s="20">
         <v>0.999999999</v>
       </c>
+      <c r="M21" s="20">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21">
@@ -1056,6 +1119,9 @@
       <c r="L22" s="21">
         <v>0.999999999</v>
       </c>
+      <c r="M22" s="21">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="22">
@@ -1094,6 +1160,9 @@
       <c r="L23" s="22">
         <v>0.999999999</v>
       </c>
+      <c r="M23" s="22">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="23">
@@ -1132,6 +1201,9 @@
       <c r="L24" s="23">
         <v>0.999999999</v>
       </c>
+      <c r="M24" s="23">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="24">
@@ -1170,6 +1242,9 @@
       <c r="L25" s="24">
         <v>0.999999999</v>
       </c>
+      <c r="M25" s="24">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="25">
@@ -1208,6 +1283,9 @@
       <c r="L26" s="25">
         <v>0.999999999</v>
       </c>
+      <c r="M26" s="25">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="26">
@@ -1246,6 +1324,9 @@
       <c r="L27" s="26">
         <v>0.999999999</v>
       </c>
+      <c r="M27" s="26">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="27">
@@ -1284,6 +1365,9 @@
       <c r="L28" s="27">
         <v>0.999999999</v>
       </c>
+      <c r="M28" s="27">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="28">
@@ -1322,6 +1406,9 @@
       <c r="L29" s="28">
         <v>0.999999999</v>
       </c>
+      <c r="M29" s="28">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="29">
@@ -1360,6 +1447,9 @@
       <c r="L30" s="29">
         <v>0.999999999</v>
       </c>
+      <c r="M30" s="29">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="30">
@@ -1398,6 +1488,9 @@
       <c r="L31" s="30">
         <v>0.999999999</v>
       </c>
+      <c r="M31" s="30">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="31">
@@ -1436,6 +1529,9 @@
       <c r="L32" s="31">
         <v>0.999999999</v>
       </c>
+      <c r="M32" s="31">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="32">
@@ -1474,6 +1570,9 @@
       <c r="L33" s="32">
         <v>0.999999999</v>
       </c>
+      <c r="M33" s="32">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="33">
@@ -1512,6 +1611,9 @@
       <c r="L34" s="33">
         <v>0.999999999</v>
       </c>
+      <c r="M34" s="33">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="34">
@@ -1550,6 +1652,9 @@
       <c r="L35" s="34">
         <v>0.999999999</v>
       </c>
+      <c r="M35" s="34">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="35">
@@ -1588,6 +1693,9 @@
       <c r="L36" s="35">
         <v>0.999999999</v>
       </c>
+      <c r="M36" s="35">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="36">
@@ -1626,6 +1734,9 @@
       <c r="L37" s="36">
         <v>0.999999999</v>
       </c>
+      <c r="M37" s="36">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="37">
@@ -1664,6 +1775,9 @@
       <c r="L38" s="37">
         <v>0.999999999</v>
       </c>
+      <c r="M38" s="37">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="38">
@@ -1702,6 +1816,9 @@
       <c r="L39" s="38">
         <v>0.999999999</v>
       </c>
+      <c r="M39" s="38">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="39">
@@ -1740,6 +1857,9 @@
       <c r="L40" s="39">
         <v>0.999999999</v>
       </c>
+      <c r="M40" s="39">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="40">
@@ -1778,6 +1898,9 @@
       <c r="L41" s="40">
         <v>0.999999999</v>
       </c>
+      <c r="M41" s="40">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="41">
@@ -1816,6 +1939,9 @@
       <c r="L42" s="41">
         <v>0.999999999</v>
       </c>
+      <c r="M42" s="41">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="42">
@@ -1854,6 +1980,9 @@
       <c r="L43" s="42">
         <v>0.999999999</v>
       </c>
+      <c r="M43" s="42">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="43">
@@ -1892,6 +2021,9 @@
       <c r="L44" s="43">
         <v>0.999999999</v>
       </c>
+      <c r="M44" s="43">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="44">
@@ -1930,6 +2062,9 @@
       <c r="L45" s="44">
         <v>0.999999999</v>
       </c>
+      <c r="M45" s="44">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="45">
@@ -1968,6 +2103,9 @@
       <c r="L46" s="45">
         <v>0.999999999</v>
       </c>
+      <c r="M46" s="45">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="46">
@@ -2006,6 +2144,9 @@
       <c r="L47" s="46">
         <v>0.999999999</v>
       </c>
+      <c r="M47" s="46">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="47">
@@ -2044,6 +2185,9 @@
       <c r="L48" s="47">
         <v>0.999999999</v>
       </c>
+      <c r="M48" s="47">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="48">
@@ -2082,6 +2226,9 @@
       <c r="L49" s="48">
         <v>0.999999999</v>
       </c>
+      <c r="M49" s="48">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="49">
@@ -2120,6 +2267,9 @@
       <c r="L50" s="49">
         <v>0.999999999</v>
       </c>
+      <c r="M50" s="49">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="50">
@@ -2158,6 +2308,9 @@
       <c r="L51" s="50">
         <v>0.999999999</v>
       </c>
+      <c r="M51" s="50">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="51">
@@ -2196,6 +2349,9 @@
       <c r="L52" s="51">
         <v>0.999999999</v>
       </c>
+      <c r="M52" s="51">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="52">
@@ -2234,6 +2390,9 @@
       <c r="L53" s="52">
         <v>0.999999999</v>
       </c>
+      <c r="M53" s="52">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="53">
@@ -2272,6 +2431,9 @@
       <c r="L54" s="53">
         <v>0.999999999</v>
       </c>
+      <c r="M54" s="53">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="54">
@@ -2310,6 +2472,9 @@
       <c r="L55" s="54">
         <v>0.999999999</v>
       </c>
+      <c r="M55" s="54">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="55">
@@ -2348,6 +2513,9 @@
       <c r="L56" s="55">
         <v>0.999999999</v>
       </c>
+      <c r="M56" s="55">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="56">
@@ -2386,6 +2554,9 @@
       <c r="L57" s="56">
         <v>0.999999999</v>
       </c>
+      <c r="M57" s="56">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="57">
@@ -2424,6 +2595,9 @@
       <c r="L58" s="57">
         <v>0.999999999</v>
       </c>
+      <c r="M58" s="57">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="58">
@@ -2462,6 +2636,9 @@
       <c r="L59" s="58">
         <v>0.999999999</v>
       </c>
+      <c r="M59" s="58">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="59">
@@ -2500,6 +2677,9 @@
       <c r="L60" s="59">
         <v>0.999999999</v>
       </c>
+      <c r="M60" s="59">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="60">
@@ -2538,6 +2718,9 @@
       <c r="L61" s="60">
         <v>0.999999999</v>
       </c>
+      <c r="M61" s="60">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="61">
@@ -2576,6 +2759,9 @@
       <c r="L62" s="61">
         <v>0.999999999</v>
       </c>
+      <c r="M62" s="61">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="62">
@@ -2614,6 +2800,9 @@
       <c r="L63" s="62">
         <v>0.999999999</v>
       </c>
+      <c r="M63" s="62">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="63">
@@ -2652,6 +2841,9 @@
       <c r="L64" s="63">
         <v>0.999999999</v>
       </c>
+      <c r="M64" s="63">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="64">
@@ -2690,6 +2882,9 @@
       <c r="L65" s="64">
         <v>0.999999999</v>
       </c>
+      <c r="M65" s="64">
+        <v>0.000000001</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="65">
@@ -2727,6 +2922,9 @@
       </c>
       <c r="L66" s="65">
         <v>0.999999999</v>
+      </c>
+      <c r="M66" s="65">
+        <v>0.000000001</v>
       </c>
     </row>
   </sheetData>
